--- a/Development/Common/GameData/MonsterAI.xlsx
+++ b/Development/Common/GameData/MonsterAI.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="21.25" customWidth="1" style="12" min="1" max="1"/>
@@ -987,6 +987,47 @@
         <v>8000</v>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="3" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DragonBoss</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>드래곤 보스 — 아레나 전역 어그로, 배회 없음. BT 완성 시 AIType=BehaviourTree 로 변경</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>FSM</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Development/Common/GameData/MonsterAI.xlsx
+++ b/Development/Common/GameData/MonsterAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1356DDF9-D635-4FD6-A82A-118B5896B90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB3F617-18F3-4B30-A2E6-4DA32A1C9518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>데이터이름</t>
   </si>
@@ -67,6 +67,18 @@
     <t>개별 스킬 사거리 무시</t>
   </si>
   <si>
+    <t>전투 위치변경 주기(ms)</t>
+  </si>
+  <si>
+    <t>전투 위치변경 최소거리</t>
+  </si>
+  <si>
+    <t>전투 위치변경 최대거리</t>
+  </si>
+  <si>
+    <t>밀집 타겟 반경</t>
+  </si>
+  <si>
     <t>컬럼설명세부</t>
   </si>
   <si>
@@ -94,6 +106,18 @@
     <t>true면 공격 상태에서 각 스킬 MaxRange를 무시</t>
   </si>
   <si>
+    <t>전투 중 이 주기마다 위치변경 시도(0=비활성)</t>
+  </si>
+  <si>
+    <t>현재 위치에서 이 거리 이상 떨어진 목적지만 선택</t>
+  </si>
+  <si>
+    <t>현재 위치 중심 NavMesh 목적지 탐색 반경</t>
+  </si>
+  <si>
+    <t>스킬 시전 직전 후보 주변 캐릭터 수를 셀 반경(0=비활성)</t>
+  </si>
+  <si>
     <t>Target</t>
   </si>
   <si>
@@ -167,6 +191,18 @@
   </si>
   <si>
     <t>IgnoreSkillRange</t>
+  </si>
+  <si>
+    <t>CombatRepositionIntervalMs</t>
+  </si>
+  <si>
+    <t>CombatRepositionMinDistance</t>
+  </si>
+  <si>
+    <t>CombatRepositionMaxDistance</t>
+  </si>
+  <si>
+    <t>TargetClusterRadius</t>
   </si>
   <si>
     <t>MeleeRusher</t>
@@ -194,18 +230,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -317,7 +346,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
@@ -326,19 +355,19 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
@@ -350,13 +379,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -576,8 +605,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="3" customWidth="1"/>
@@ -587,11 +616,19 @@
     <col min="6" max="6" width="35.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.75" style="3" customWidth="1"/>
     <col min="8" max="8" width="22.875" style="3" customWidth="1"/>
-    <col min="9" max="13" width="32" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="9" max="9" width="32" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.375" customWidth="1"/>
+    <col min="14" max="14" width="30.625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="30.625" customWidth="1"/>
+    <col min="16" max="16" width="28.375" customWidth="1"/>
+    <col min="17" max="17" width="26.375" customWidth="1"/>
+    <col min="18" max="16384" width="13" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -639,129 +676,177 @@
       <c r="M2" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="N2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>33</v>
+        <v>41</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -771,10 +856,14 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -806,60 +895,84 @@
       <c r="M7" s="8" t="b">
         <v>0</v>
       </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3">
         <v>10</v>
@@ -885,19 +998,31 @@
       <c r="M9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3">
         <v>12</v>
@@ -923,19 +1048,31 @@
       <c r="M10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>1003</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3">
         <v>35</v>
@@ -961,9 +1098,21 @@
       <c r="M11" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="N11" s="3">
+        <v>12000</v>
+      </c>
+      <c r="O11" s="3">
+        <v>8</v>
+      </c>
+      <c r="P11" s="3">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>